--- a/check_iot_ai.xlsx
+++ b/check_iot_ai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutoReport_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886ED5AD-C0FC-4669-B148-2CAB3ED35F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED27F33-329A-4827-83E9-94FB668B7965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" tabRatio="384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" tabRatio="426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IOT Device" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="185">
   <si>
     <t>分類</t>
   </si>
@@ -80,6 +80,9 @@
     <t>cvss</t>
   </si>
   <si>
+    <t>score</t>
+  </si>
+  <si>
     <t>Static</t>
   </si>
   <si>
@@ -92,16 +95,25 @@
     <t>Not Applicable</t>
   </si>
   <si>
-    <t>無提供</t>
-  </si>
-  <si>
     <t>S02</t>
   </si>
   <si>
     <t>SBOM Vulnerability Scanning</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>None</t>
+  </si>
+  <si>
+    <t>測試方式：
+- 依「SBOM」分頁所列軟體元件與版本進行公開弱點資訊檢視。
+測試結果：
+- SBOM 分頁所列 CCRL 1.02.00.00 與 1.07.00.00 均註記「未發現可確認之公開 CVE」。
+攻擊條件：
+- 目前未發現可確認之公開 CVE，因此未識別明確的已知漏洞攻擊條件。
+可能影響：
+- 目前未發現可由已知公開 CVE 確認的元件弱點風險。
+既有防護／限制條件：
+- 本次結果以 SBOM 分頁已列元件、版本及可取得之公開 CVE 資訊為評估範圍。</t>
   </si>
   <si>
     <t>Dynamic</t>
@@ -113,7 +125,16 @@
     <t>Sandbox Test</t>
   </si>
   <si>
-    <t>None</t>
+    <t>測試方式：
+- 操作裝置並進行測量，觀察裝置執行期間是否出現異常。
+測試結果：
+- 測試過程未發生異常。
+攻擊條件：
+- 本次測試未觀察到可進一步形成攻擊情境的異常行為。
+可能影響：
+- 本次測試未發現可確認之異常影響。
+既有防護／限制條件：
+- 原始資料未提供其他防護或限制條件。</t>
   </si>
   <si>
     <t>Fuzzing</t>
@@ -125,7 +146,16 @@
     <t>Fuzzing Test</t>
   </si>
   <si>
-    <t>透過nRF進行藍牙配對及資料寫入 (如超長字串、特殊字元等) 無發生系統當機，無發現異常。</t>
+    <t>測試方式：
+- 透過 nRF 進行藍牙配對及資料寫入，包含超長字串、特殊字元等異常輸入。
+測試結果：
+- 測試期間未發生系統當機，亦未發現其他異常。
+攻擊條件：
+- 需能透過藍牙連線對裝置進行資料寫入。
+可能影響：
+- 本次異常輸入測試未觀察到可確認之系統異常或可利用行為。
+既有防護／限制條件：
+- 本次結果以已執行的藍牙配對與資料寫入測試案例為範圍。</t>
   </si>
   <si>
     <t>PT</t>
@@ -137,13 +167,34 @@
     <t>Device Vulnerability Scanning</t>
   </si>
   <si>
+    <t>測試方式：
+- 確認裝置是否具備可供主機弱點掃描之介面。
+測試結果：
+- 此裝置為 IoT 設備，未提供主機弱點掃描介面，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；未具備本測項所需之主機掃描介面。
+可能影響：
+- 本次未執行主機層弱點掃描，故無法由此測項評估主機服務弱點。
+既有防護／限制條件：
+- 評估範圍受限於裝置介面設計。</t>
+  </si>
+  <si>
     <t>P02          </t>
   </si>
   <si>
     <t>UI Vulnerability Scanning</t>
   </si>
   <si>
-    <t>介面僅按鈕操作，無web 介面</t>
+    <t>測試方式：
+- 確認裝置是否具有可進行 UI/Web 弱點掃描之介面。
+測試結果：
+- 裝置介面僅提供按鈕操作，無 Web 介面，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；裝置未提供 Web UI。
+可能影響：
+- 本次未識別 Web UI 相關攻擊面。
+既有防護／限制條件：
+- 使用介面僅限裝置按鈕操作。</t>
   </si>
   <si>
     <t>P03          </t>
@@ -152,7 +203,16 @@
     <t>Authentication (Remote)</t>
   </si>
   <si>
-    <t>無網路介面</t>
+    <t>測試方式：
+- 確認裝置是否具備可供遠端身分驗證之網路介面。
+測試結果：
+- 裝置無網路介面，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；未提供遠端網路介面。
+可能影響：
+- 本次未識別遠端網路身分驗證攻擊面。
+既有防護／限制條件：
+- 裝置無網路介面。</t>
   </si>
   <si>
     <t>P04          </t>
@@ -161,7 +221,16 @@
     <t>Authentication (Local)</t>
   </si>
   <si>
-    <t>單機使用，不需認證</t>
+    <t>測試方式：
+- 確認裝置本地操作是否需要身分驗證。
+測試結果：
+- 裝置為單機使用情境，原始資料記載不需認證。
+攻擊條件：
+- 原始資料未提供需透過帳號或本地身分驗證控制的使用情境。
+可能影響：
+- 本次未發現可由本地帳號認證機制確認之風險。
+既有防護／限制條件：
+- 裝置採單機使用，且原始資料未描述多使用者或帳號權限情境。</t>
   </si>
   <si>
     <t>P05          </t>
@@ -170,6 +239,18 @@
     <t>Network Security Test (Remote)</t>
   </si>
   <si>
+    <t>測試方式：
+- 確認裝置是否具有可進行遠端網路安全測試之介面。
+測試結果：
+- 裝置無網路介面，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；未提供遠端網路介面。
+可能影響：
+- 本次未識別遠端網路服務之攻擊面。
+既有防護／限制條件：
+- 裝置無網路介面。</t>
+  </si>
+  <si>
     <t>P06          </t>
   </si>
   <si>
@@ -179,11 +260,21 @@
     <t>Low</t>
   </si>
   <si>
-    <t>藍牙側錄：
-1.藍牙版本5.1
-2.有開啟傳輸加密
-3.對應CVE參考"藍牙5.1 CVE list" (高風險)
-藍牙由裝置發起配對，為Just Works模式，不必輸入配對資訊(PIN Code / Passkey)，但因為藍牙由裝置按鈕進行人工啟動，非長時間開啟，且傳輸敏感性資料有進行加密，判斷為低風險</t>
+    <t>測試方式：
+- 進行藍牙通訊側錄與配對流程確認，並參考「藍牙5.1 CVE list」分頁檢視相關公開弱點資訊。
+測試結果：
+- 藍牙版本為 5.1。
+- 傳輸過程有啟用加密。
+- 裝置發起配對時採 Just Works 模式，不需輸入 PIN Code／Passkey。
+- 「藍牙5.1 CVE list」分頁包含高風險項目，實際適用性仍需依使用之藍牙堆疊、實作與版本確認。
+攻擊條件：
+- 攻擊者需位於藍牙通訊範圍內。
+- 裝置藍牙需由使用者按下實體按鈕後人工啟動，並非長時間持續開啟。
+可能影響：
+- Just Works 配對不要求 PIN Code／Passkey；若相關配對或藍牙協定弱點適用，可能存在未經充分身分驗證之配對、通訊攔截或資料遭未授權存取的風險。
+既有防護／限制條件：
+- 藍牙由裝置實體按鈕人工啟動，非長時間開啟。
+- 傳輸敏感性資料時已有加密保護。</t>
   </si>
   <si>
     <t>P07          </t>
@@ -192,7 +283,16 @@
     <t>Minimize Network Service</t>
   </si>
   <si>
-    <t>僅提供藍牙服務，參考P06</t>
+    <t>測試方式：
+- 確認裝置對外提供之網路／無線通訊服務，並參考 P06 藍牙測試結果。
+測試結果：
+- 裝置僅提供藍牙服務。
+攻擊條件：
+- 相關攻擊需透過裝置所提供的藍牙通訊介面，其他條件參考 P06。
+可能影響：
+- 本次未發現除藍牙外的其他網路服務攻擊面。
+既有防護／限制條件：
+- 對外服務範圍僅限藍牙，相關藍牙啟用與傳輸限制參考 P06。</t>
   </si>
   <si>
     <t>P08          </t>
@@ -201,7 +301,17 @@
     <t>Sensitive Data Leakage</t>
   </si>
   <si>
-    <t>資料僅能透過藍牙傳輸，藍牙傳輸時資料有加密，參考P06</t>
+    <t>測試方式：
+- 確認敏感性資料之傳輸方式與傳輸保護情形，並參考 P06 藍牙測試結果。
+測試結果：
+- 資料僅透過藍牙傳輸，藍牙傳輸時資料有加密。
+攻擊條件：
+- 需位於藍牙通訊範圍內，且在裝置藍牙啟用期間進行攻擊；其他配對條件參考 P06。
+可能影響：
+- 若藍牙配對或傳輸保護機制遭利用，可能造成敏感性資料遭未授權存取或暴露。
+既有防護／限制條件：
+- 敏感性資料傳輸已有加密保護。
+- 藍牙非長時間開啟，啟用條件參考 P06。</t>
   </si>
   <si>
     <t>P09          </t>
@@ -210,7 +320,18 @@
     <t>API Authentication</t>
   </si>
   <si>
-    <t>參考P06</t>
+    <t>測試方式：
+- 本測項依 P06 所述藍牙配對與連線機制進行判定。
+測試結果：
+- 參考 P06：裝置採 Just Works 配對模式，不需輸入 PIN Code／Passkey。
+- 原始資料未另外提供獨立 API 驗證流程或介面細節。
+攻擊條件：
+- 需位於藍牙通訊範圍內，且裝置需處於藍牙啟用／配對情境；其他條件參考 P06。
+可能影響：
+- 在 Just Works 配對情境下，身分確認能力較有限，可能存在未經充分驗證之存取風險；實際 API 權限與可存取範圍仍需依產品實作確認。
+既有防護／限制條件：
+- 藍牙由裝置實體按鈕人工啟動，非長時間開啟。
+- 傳輸敏感性資料時已有加密保護，相關內容參考 P06。</t>
   </si>
   <si>
     <t>P10          </t>
@@ -219,7 +340,16 @@
     <t>API Input Validation</t>
   </si>
   <si>
-    <t>參考F01</t>
+    <t>測試方式：
+- 參考 F01，透過 nRF 進行藍牙配對及資料寫入，包含超長字串、特殊字元等異常輸入。
+測試結果：
+- 參考 F01：測試期間未發生系統當機，亦未發現其他異常。
+攻擊條件：
+- 需能透過藍牙連線對裝置進行資料寫入。
+可能影響：
+- 本次異常輸入測試未觀察到可確認之輸入驗證異常或可利用行為。
+既有防護／限制條件：
+- 本次結果以 F01 已執行之藍牙資料寫入與異常輸入測試案例為範圍。</t>
   </si>
   <si>
     <t>P11          </t>
@@ -228,7 +358,16 @@
     <t>UI: Default Password</t>
   </si>
   <si>
-    <t>無帳號密碼設定功能</t>
+    <t>測試方式：
+- 確認裝置是否具有帳號密碼與預設密碼功能。
+測試結果：
+- 裝置無帳號密碼設定功能，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；未提供帳號密碼功能。
+可能影響：
+- 本次未識別預設密碼相關攻擊面。
+既有防護／限制條件：
+- 裝置無帳號密碼設定功能。</t>
   </si>
   <si>
     <t>P12          </t>
@@ -237,19 +376,52 @@
     <t>UI: Password Strength</t>
   </si>
   <si>
+    <t>測試方式：
+- 確認裝置是否具有帳號密碼設定及密碼強度要求。
+測試結果：
+- 裝置無帳號密碼設定功能，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；未提供帳號密碼功能。
+可能影響：
+- 本次未識別密碼強度相關攻擊面。
+既有防護／限制條件：
+- 裝置無帳號密碼設定功能。</t>
+  </si>
+  <si>
     <t>P13          </t>
   </si>
   <si>
     <t>UI: Password Management</t>
   </si>
   <si>
+    <t>測試方式：
+- 確認裝置是否具有帳號密碼管理功能。
+測試結果：
+- 裝置無帳號密碼設定功能，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；未提供帳號密碼功能。
+可能影響：
+- 本次未識別密碼管理相關攻擊面。
+既有防護／限制條件：
+- 裝置無帳號密碼設定功能。</t>
+  </si>
+  <si>
     <t>P14          </t>
   </si>
   <si>
     <t>UI: Configuration Management</t>
   </si>
   <si>
-    <t>介面僅能根據韌體的設計選取對應的功能。無法進行額外設定。</t>
+    <t>測試方式：
+- 確認裝置使用介面可進行的設定與功能選項。
+測試結果：
+- 介面僅能依韌體設計選取對應功能，無法進行額外設定。
+攻擊條件：
+- 原始資料未提供可由使用者任意修改安全設定的介面或情境。
+可能影響：
+- 本次未發現可由額外組態修改造成的可確認風險。
+既有防護／限制條件：
+- 使用者可操作之設定範圍受韌體既定功能限制。</t>
   </si>
   <si>
     <t>P15          </t>
@@ -258,7 +430,16 @@
     <t>Security Event Logging</t>
   </si>
   <si>
-    <t>無相關設計</t>
+    <t>測試方式：
+- 確認產品是否具有 Security Event Logging 相關設計。
+測試結果：
+- 原始資料記載「無相關設計」，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；本次無相關日誌功能可供測試。
+可能影響：
+- 本次未針對安全事件日誌能力進行功能性驗證。
+既有防護／限制條件：
+- 產品目前無相關設計。</t>
   </si>
   <si>
     <t>P16          </t>
@@ -267,13 +448,34 @@
     <t>Security Event Notification</t>
   </si>
   <si>
+    <t>測試方式：
+- 確認產品是否具有 Security Event Notification 相關設計。
+測試結果：
+- 原始資料記載「無相關設計」，因此本測項判定為 Not Applicable。
+攻擊條件：
+- 不適用；本次無相關事件通知功能可供測試。
+可能影響：
+- 本次未針對安全事件通知能力進行功能性驗證。
+既有防護／限制條件：
+- 產品目前無相關設計。</t>
+  </si>
+  <si>
     <t>P17          </t>
   </si>
   <si>
     <t>Application Update</t>
   </si>
   <si>
-    <t>召回</t>
+    <t>測試方式：
+- 確認產品於 Application Update 測項之處理方式。
+測試結果：
+- 原始資料記載更新處理方式為「召回」。
+攻擊條件：
+- 原始資料未提供可進一步判定之線上或本地更新攻擊情境。
+可能影響：
+- 因未提供其他更新流程細節，本次無法由此測項進一步評估更新機制之攻擊面。
+既有防護／限制條件：
+- 產品更新處理由召回方式進行；原始資料未提供其他更新機制資訊。</t>
   </si>
   <si>
     <t>P18          </t>
@@ -282,18 +484,54 @@
     <t>Application Delivery Protection</t>
   </si>
   <si>
+    <t>測試方式：
+- 確認產品於 Application Delivery Protection 測項之處理方式。
+測試結果：
+- 原始資料記載處理方式為「召回」。
+攻擊條件：
+- 原始資料未提供可進一步判定之應用程式交付或更新通道攻擊情境。
+可能影響：
+- 因未提供其他交付流程細節，本次無法由此測項進一步評估軟體交付保護之攻擊面。
+既有防護／限制條件：
+- 產品相關處理由召回方式進行；原始資料未提供其他交付保護機制資訊。</t>
+  </si>
+  <si>
     <t>P19          </t>
   </si>
   <si>
     <t>Static Application Analysis</t>
   </si>
   <si>
+    <t>測試方式：
+- 針對 MCU 及藍牙韌體進行敏感性字串偵蒐。
+測試結果：
+- MCU 與藍牙韌體皆未發現敏感性關鍵字，因此原始資料評估為無風險。
+攻擊條件：
+- 本次未發現可由敏感性字串暴露形成的明確攻擊情境。
+可能影響：
+- 本次未發現可確認之敏感性資訊字串暴露風險。
+既有防護／限制條件：
+- 本次結果以已執行之 MCU 與藍牙韌體敏感性字串偵蒐範圍為限。</t>
+  </si>
+  <si>
     <t>P20</t>
   </si>
   <si>
     <t>Physical Protection</t>
   </si>
   <si>
+    <t>測試方式：
+- 確認裝置是否具備防止韌體遭直接讀取之實體／晶片層保護設定。
+測試結果：
+- 廠商提供 Read Protection 防止韌體讀取設定，因此原始資料評估為無風險。
+攻擊條件：
+- 若攻擊者嘗試透過可接觸之裝置介面讀取韌體，將受到 Read Protection 設定限制。
+可能影響：
+- 本次未發現可確認之韌體直接讀取風險。
+既有防護／限制條件：
+- 已提供 Read Protection 防止韌體讀取。</t>
+  </si>
+  <si>
     <t>最高風險</t>
   </si>
   <si>
@@ -349,9 +587,6 @@
   </si>
   <si>
     <t>1.07.00.00</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>風險值</t>
@@ -573,76 +808,28 @@
     <t>Critical</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
+    <t>TBD</t>
+  </si>
+  <si>
     <t>Testing</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>此裝置為</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>iot</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>設備，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>主機弱掃介面</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.操作裝置，進行測量，無發生異常。
-</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>score</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>針對 MCU及藍牙韌體進行敏感性字串偵蒐，兩者皆無發現任何敏感性關鍵字，故評估為無風險。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>廠商提供 Read Protection防止韌體讀取設定，故評估為無風險。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>參考SBOM分頁</t>
+    <t>測試方式：
+- 本次未執行 Source code scanning。
+測試結果：
+- 無提供，未取得執行本測項所需資料，因此判定為 Not Applicable。
+攻擊條件：
+- 不適用；本測項未進入弱點驗證階段。
+可能影響：
+- 因未執行原始碼掃描，本次無法由此測項確認原始碼層級之潛在弱點。
+既有防護／限制條件：
+- 本次評估範圍受限於未提供本測項所需資料。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -650,10 +837,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="38">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -732,21 +916,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
@@ -769,13 +938,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
@@ -783,35 +945,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF7030A0"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="9"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="9"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
@@ -896,29 +1029,22 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Microsoft JhengHei UI"/>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Microsoft JhengHei"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1001,12 +1127,6 @@
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1104,7 +1224,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1146,174 +1266,124 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1322,6 +1392,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1612,627 +1689,630 @@
     <col min="2" max="2" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47.23046875" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="69.4609375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="74.84375" style="1" customWidth="1"/>
     <col min="6" max="6" width="46.3828125" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.3828125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.84375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.53515625" style="1" customWidth="1"/>
     <col min="9" max="10" width="35.69140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="52.69140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.15234375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.69140625" style="1"/>
+    <col min="13" max="13" width="8.69140625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.69140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="15" customFormat="1" ht="15.9" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:12" s="63" customFormat="1" ht="26.6" customHeight="1">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="18" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="150" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="L1" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="20" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="C2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="D2" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-    </row>
-    <row r="3" spans="1:12" ht="150" customHeight="1">
-      <c r="A3" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="E2" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="F3" s="41"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-    </row>
-    <row r="4" spans="1:12" ht="150" customHeight="1">
-      <c r="A4" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="75"/>
-    </row>
-    <row r="5" spans="1:12" ht="150" customHeight="1">
-      <c r="A5" s="24" t="s">
+      <c r="D4" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="B5" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="40" t="s">
+      <c r="C5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="45"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="75"/>
-    </row>
-    <row r="6" spans="1:12" ht="150" customHeight="1">
-      <c r="A6" s="27" t="s">
+      <c r="D5" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="B6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-    </row>
-    <row r="7" spans="1:12" ht="150" customHeight="1">
-      <c r="A7" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="C6" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="D6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="33" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-    </row>
-    <row r="8" spans="1:12" ht="150" customHeight="1">
-      <c r="A8" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="28" t="s">
+      <c r="C7" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="D7" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="33" t="s">
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+    </row>
+    <row r="8" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-    </row>
-    <row r="9" spans="1:12" ht="150" customHeight="1">
-      <c r="A9" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="28" t="s">
+      <c r="C8" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="D8" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="30" t="s">
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="75"/>
-    </row>
-    <row r="10" spans="1:12" ht="150" customHeight="1">
-      <c r="A10" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="28" t="s">
+      <c r="C9" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="D9" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-    </row>
-    <row r="11" spans="1:12" ht="150" customHeight="1">
-      <c r="A11" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="28" t="s">
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C10" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D10" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-    </row>
-    <row r="12" spans="1:12" ht="150" customHeight="1">
-      <c r="A12" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="28" t="s">
+      <c r="C11" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="D11" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="40" t="s">
+      <c r="E11" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="75"/>
-    </row>
-    <row r="13" spans="1:12" ht="150" customHeight="1">
-      <c r="A13" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="28" t="s">
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A12" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C12" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="40" t="s">
+      <c r="D12" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-    </row>
-    <row r="14" spans="1:12" ht="150" customHeight="1">
-      <c r="A14" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="28" t="s">
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A13" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="33" t="s">
+      <c r="D13" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-    </row>
-    <row r="15" spans="1:12" ht="150" customHeight="1">
-      <c r="A15" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="28" t="s">
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C14" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="33" t="s">
+      <c r="D14" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="75"/>
-    </row>
-    <row r="16" spans="1:12" ht="150" customHeight="1">
-      <c r="A16" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A15" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C15" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="33" t="s">
+      <c r="D15" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-    </row>
-    <row r="17" spans="1:12" ht="150" customHeight="1">
-      <c r="A17" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="28" t="s">
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A16" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C16" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-    </row>
-    <row r="18" spans="1:12" ht="150" customHeight="1">
-      <c r="A18" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="D16" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+    </row>
+    <row r="17" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A17" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
-    </row>
-    <row r="19" spans="1:12" ht="150" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="28" t="s">
+      <c r="C17" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="D17" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="21" t="s">
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+    </row>
+    <row r="18" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A18" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="75"/>
-    </row>
-    <row r="20" spans="1:12" ht="150" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="28" t="s">
+      <c r="C18" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="D18" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="33" t="s">
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+    </row>
+    <row r="19" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48"/>
-    </row>
-    <row r="21" spans="1:12" ht="150" customHeight="1">
-      <c r="A21" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="28" t="s">
+      <c r="C19" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="D19" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="48"/>
-    </row>
-    <row r="22" spans="1:12" ht="150" customHeight="1">
-      <c r="A22" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="28" t="s">
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+    </row>
+    <row r="20" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C20" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="33" t="s">
+      <c r="D20" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="75"/>
-    </row>
-    <row r="23" spans="1:12" ht="150" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="28" t="s">
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+    </row>
+    <row r="21" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A21" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C21" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="41"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="75"/>
-    </row>
-    <row r="24" spans="1:12" ht="150" customHeight="1">
-      <c r="A24" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="28" t="s">
+      <c r="D21" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+    </row>
+    <row r="22" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="75"/>
-    </row>
-    <row r="25" spans="1:12" ht="150" customHeight="1">
-      <c r="A25" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="28" t="s">
+      <c r="C22" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="D22" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+    </row>
+    <row r="23" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A23" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+    </row>
+    <row r="24" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A24" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" spans="1:12" ht="200.05" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="1:12">
       <c r="B26" s="7"/>
@@ -2242,7 +2322,7 @@
     <row r="27" spans="1:12" ht="15.45" customHeight="1">
       <c r="D27" s="12"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="46"/>
+      <c r="F27" s="31"/>
       <c r="G27" s="9"/>
     </row>
     <row r="28" spans="1:12" ht="15.45" customHeight="1">
@@ -9603,57 +9683,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>84</v>
+      <c r="B1" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
+      <c r="A3" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
+      <c r="A4" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
+      <c r="A5" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -9684,84 +9764,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18.45" customHeight="1">
-      <c r="B1" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="43"/>
+      <c r="B1" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B2" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="J2" s="53" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="53" t="s">
+      <c r="B2" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="C2" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="42"/>
+      <c r="M2" s="28"/>
     </row>
     <row r="3" spans="2:13" ht="18" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="2:13" ht="18" customHeight="1">
-      <c r="B4" s="47"/>
-      <c r="C4" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -9774,423 +9854,423 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="12.23046875" style="68" customWidth="1"/>
-    <col min="2" max="2" width="46.53515625" style="68" customWidth="1"/>
-    <col min="3" max="3" width="22.4609375" style="68" customWidth="1"/>
-    <col min="4" max="4" width="8.4609375" style="68" customWidth="1"/>
-    <col min="5" max="5" width="43.53515625" style="68" customWidth="1"/>
-    <col min="6" max="6" width="50.4609375" style="68" customWidth="1"/>
-    <col min="7" max="7" width="23.84375" style="68" customWidth="1"/>
-    <col min="8" max="8" width="54.4609375" style="68" customWidth="1"/>
-    <col min="9" max="9" width="20.15234375" style="74" customWidth="1"/>
-    <col min="10" max="11" width="8.69140625" style="68" customWidth="1"/>
-    <col min="12" max="16384" width="8.69140625" style="68"/>
+    <col min="1" max="1" width="12.23046875" style="51" customWidth="1"/>
+    <col min="2" max="2" width="46.53515625" style="51" customWidth="1"/>
+    <col min="3" max="3" width="22.4609375" style="51" customWidth="1"/>
+    <col min="4" max="4" width="8.4609375" style="51" customWidth="1"/>
+    <col min="5" max="5" width="43.53515625" style="51" customWidth="1"/>
+    <col min="6" max="6" width="50.4609375" style="51" customWidth="1"/>
+    <col min="7" max="7" width="23.84375" style="51" customWidth="1"/>
+    <col min="8" max="8" width="54.4609375" style="51" customWidth="1"/>
+    <col min="9" max="9" width="20.15234375" style="57" customWidth="1"/>
+    <col min="10" max="12" width="8.69140625" style="51" customWidth="1"/>
+    <col min="13" max="16384" width="8.69140625" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="55" customFormat="1" ht="18.45" customHeight="1">
-      <c r="A1" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="57"/>
-      <c r="E1" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="I1" s="58" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="55" customFormat="1" ht="18.45" customHeight="1">
-      <c r="A2" s="59" t="s">
+    <row r="1" spans="1:9" s="38" customFormat="1" ht="18.45" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B1" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="60" t="str">
+      <c r="D1" s="40"/>
+      <c r="E1" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="I1" s="41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="38" customFormat="1" ht="18.45" customHeight="1">
+      <c r="A2" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="43" t="str">
         <f t="shared" ref="D2:D14" si="0">HYPERLINK(CONCATENATE("https://nvd.nist.gov/vuln/detail/", C2), "🔗")</f>
         <v>🔗</v>
       </c>
-      <c r="E2" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" s="59"/>
+      <c r="E2" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="30.9" customHeight="1">
-      <c r="A3" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="64" t="str">
+      <c r="A3" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E3" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="H3" s="67" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="59" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="55" customFormat="1" ht="18.45" customHeight="1">
-      <c r="A4" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="59" t="s">
+      <c r="E3" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="38" customFormat="1" ht="18.45" customHeight="1">
+      <c r="A4" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="60" t="str">
+      <c r="B4" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E4" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="G4" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="H4" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="I4" s="59"/>
-    </row>
-    <row r="5" spans="1:9" s="55" customFormat="1" ht="30.9" customHeight="1">
-      <c r="A5" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="64" t="str">
+      <c r="E4" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="42"/>
+    </row>
+    <row r="5" spans="1:9" s="38" customFormat="1" ht="30.9" customHeight="1">
+      <c r="A5" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E5" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="65" t="s">
-        <v>130</v>
-      </c>
-      <c r="H5" s="67" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" s="59" t="s">
-        <v>123</v>
+      <c r="E5" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="77.150000000000006" customHeight="1">
-      <c r="A6" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="63" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="64" t="str">
+      <c r="A6" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E6" s="65" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="H6" s="67" t="s">
-        <v>136</v>
-      </c>
-      <c r="I6" s="59"/>
+      <c r="E6" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="H6" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9" ht="61.75" customHeight="1">
-      <c r="A7" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="64" t="str">
+      <c r="A7" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E7" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="69" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="H7" s="65" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" s="59" t="s">
-        <v>123</v>
+      <c r="E7" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.45" customHeight="1">
-      <c r="A8" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="59" t="s">
+      <c r="A8" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="60" t="str">
+      <c r="B8" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E8" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="G8" s="59" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="70" t="s">
-        <v>144</v>
-      </c>
-      <c r="I8" s="59"/>
+      <c r="E8" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="I8" s="42"/>
     </row>
     <row r="9" spans="1:9" ht="30.9" customHeight="1">
-      <c r="A9" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>145</v>
-      </c>
-      <c r="D9" s="64" t="str">
+      <c r="A9" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E9" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>147</v>
-      </c>
-      <c r="H9" s="67" t="s">
-        <v>148</v>
-      </c>
-      <c r="I9" s="59" t="s">
-        <v>123</v>
+      <c r="E9" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="92.6" customHeight="1">
-      <c r="A10" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="59" t="s">
+      <c r="A10" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="60" t="str">
+      <c r="B10" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E10" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="G10" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="I10" s="59"/>
+      <c r="E10" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="1:9" ht="77.150000000000006" customHeight="1">
-      <c r="A11" s="71" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="64" t="str">
+      <c r="A11" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E11" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="H11" s="67" t="s">
-        <v>156</v>
-      </c>
-      <c r="I11" s="59" t="s">
-        <v>123</v>
+      <c r="E11" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30.9" customHeight="1">
-      <c r="A12" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="60" t="str">
+      <c r="A12" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E12" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="F12" s="70" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="H12" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="I12" s="59"/>
+      <c r="E12" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:9" ht="46.3" customHeight="1">
-      <c r="A13" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B13" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="D13" s="60" t="str">
+      <c r="A13" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E13" s="59" t="s">
-        <v>163</v>
-      </c>
-      <c r="F13" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="G13" s="59" t="s">
-        <v>165</v>
-      </c>
-      <c r="H13" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="I13" s="59"/>
+      <c r="E13" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9" ht="46.3" customHeight="1">
-      <c r="A14" s="59" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="59" t="s">
-        <v>167</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="D14" s="60" t="str">
+      <c r="A14" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
-      <c r="E14" s="59" t="s">
-        <v>163</v>
-      </c>
-      <c r="F14" s="70" t="s">
-        <v>169</v>
-      </c>
-      <c r="G14" s="59" t="s">
-        <v>165</v>
-      </c>
-      <c r="H14" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="I14" s="59"/>
+      <c r="E14" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="I14" s="42"/>
     </row>
     <row r="17" spans="1:2" ht="15.9" customHeight="1">
-      <c r="A17" s="72"/>
-      <c r="B17" s="73"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -10230,42 +10310,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="14.15" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="14.15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="14.15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="14.15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="14.15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="14.15" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="14.15" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="14.15" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14.15" customHeight="1">

--- a/check_iot_ai.xlsx
+++ b/check_iot_ai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutoReport_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED27F33-329A-4827-83E9-94FB668B7965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B50C46F-A66D-44E2-AB5E-68A0F5E8B8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" tabRatio="426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,18 +104,6 @@
     <t>None</t>
   </si>
   <si>
-    <t>測試方式：
-- 依「SBOM」分頁所列軟體元件與版本進行公開弱點資訊檢視。
-測試結果：
-- SBOM 分頁所列 CCRL 1.02.00.00 與 1.07.00.00 均註記「未發現可確認之公開 CVE」。
-攻擊條件：
-- 目前未發現可確認之公開 CVE，因此未識別明確的已知漏洞攻擊條件。
-可能影響：
-- 目前未發現可由已知公開 CVE 確認的元件弱點風險。
-既有防護／限制條件：
-- 本次結果以 SBOM 分頁已列元件、版本及可取得之公開 CVE 資訊為評估範圍。</t>
-  </si>
-  <si>
     <t>Dynamic</t>
   </si>
   <si>
@@ -125,18 +113,6 @@
     <t>Sandbox Test</t>
   </si>
   <si>
-    <t>測試方式：
-- 操作裝置並進行測量，觀察裝置執行期間是否出現異常。
-測試結果：
-- 測試過程未發生異常。
-攻擊條件：
-- 本次測試未觀察到可進一步形成攻擊情境的異常行為。
-可能影響：
-- 本次測試未發現可確認之異常影響。
-既有防護／限制條件：
-- 原始資料未提供其他防護或限制條件。</t>
-  </si>
-  <si>
     <t>Fuzzing</t>
   </si>
   <si>
@@ -146,18 +122,6 @@
     <t>Fuzzing Test</t>
   </si>
   <si>
-    <t>測試方式：
-- 透過 nRF 進行藍牙配對及資料寫入，包含超長字串、特殊字元等異常輸入。
-測試結果：
-- 測試期間未發生系統當機，亦未發現其他異常。
-攻擊條件：
-- 需能透過藍牙連線對裝置進行資料寫入。
-可能影響：
-- 本次異常輸入測試未觀察到可確認之系統異常或可利用行為。
-既有防護／限制條件：
-- 本次結果以已執行的藍牙配對與資料寫入測試案例為範圍。</t>
-  </si>
-  <si>
     <t>PT</t>
   </si>
   <si>
@@ -167,88 +131,28 @@
     <t>Device Vulnerability Scanning</t>
   </si>
   <si>
-    <t>測試方式：
-- 確認裝置是否具備可供主機弱點掃描之介面。
-測試結果：
-- 此裝置為 IoT 設備，未提供主機弱點掃描介面，因此本測項判定為 Not Applicable。
-攻擊條件：
-- 不適用；未具備本測項所需之主機掃描介面。
-可能影響：
-- 本次未執行主機層弱點掃描，故無法由此測項評估主機服務弱點。
-既有防護／限制條件：
-- 評估範圍受限於裝置介面設計。</t>
-  </si>
-  <si>
     <t>P02          </t>
   </si>
   <si>
     <t>UI Vulnerability Scanning</t>
   </si>
   <si>
-    <t>測試方式：
-- 確認裝置是否具有可進行 UI/Web 弱點掃描之介面。
-測試結果：
-- 裝置介面僅提供按鈕操作，無 Web 介面，因此本測項判定為 Not Applicable。
-攻擊條件：
-- 不適用；裝置未提供 Web UI。
-可能影響：
-- 本次未識別 Web UI 相關攻擊面。
-既有防護／限制條件：
-- 使用介面僅限裝置按鈕操作。</t>
-  </si>
-  <si>
     <t>P03          </t>
   </si>
   <si>
     <t>Authentication (Remote)</t>
   </si>
   <si>
-    <t>測試方式：
-- 確認裝置是否具備可供遠端身分驗證之網路介面。
-測試結果：
-- 裝置無網路介面，因此本測項判定為 Not Applicable。
-攻擊條件：
-- 不適用；未提供遠端網路介面。
-可能影響：
-- 本次未識別遠端網路身分驗證攻擊面。
-既有防護／限制條件：
-- 裝置無網路介面。</t>
-  </si>
-  <si>
     <t>P04          </t>
   </si>
   <si>
     <t>Authentication (Local)</t>
   </si>
   <si>
-    <t>測試方式：
-- 確認裝置本地操作是否需要身分驗證。
-測試結果：
-- 裝置為單機使用情境，原始資料記載不需認證。
-攻擊條件：
-- 原始資料未提供需透過帳號或本地身分驗證控制的使用情境。
-可能影響：
-- 本次未發現可由本地帳號認證機制確認之風險。
-既有防護／限制條件：
-- 裝置採單機使用，且原始資料未描述多使用者或帳號權限情境。</t>
-  </si>
-  <si>
     <t>P05          </t>
   </si>
   <si>
     <t>Network Security Test (Remote)</t>
-  </si>
-  <si>
-    <t>測試方式：
-- 確認裝置是否具有可進行遠端網路安全測試之介面。
-測試結果：
-- 裝置無網路介面，因此本測項判定為 Not Applicable。
-攻擊條件：
-- 不適用；未提供遠端網路介面。
-可能影響：
-- 本次未識別遠端網路服務之攻擊面。
-既有防護／限制條件：
-- 裝置無網路介面。</t>
   </si>
   <si>
     <t>P06          </t>
@@ -283,18 +187,6 @@
     <t>Minimize Network Service</t>
   </si>
   <si>
-    <t>測試方式：
-- 確認裝置對外提供之網路／無線通訊服務，並參考 P06 藍牙測試結果。
-測試結果：
-- 裝置僅提供藍牙服務。
-攻擊條件：
-- 相關攻擊需透過裝置所提供的藍牙通訊介面，其他條件參考 P06。
-可能影響：
-- 本次未發現除藍牙外的其他網路服務攻擊面。
-既有防護／限制條件：
-- 對外服務範圍僅限藍牙，相關藍牙啟用與傳輸限制參考 P06。</t>
-  </si>
-  <si>
     <t>P08          </t>
   </si>
   <si>
@@ -340,496 +232,876 @@
     <t>API Input Validation</t>
   </si>
   <si>
-    <t>測試方式：
+    <t>P11          </t>
+  </si>
+  <si>
+    <t>UI: Default Password</t>
+  </si>
+  <si>
+    <t>P12          </t>
+  </si>
+  <si>
+    <t>UI: Password Strength</t>
+  </si>
+  <si>
+    <t>P13          </t>
+  </si>
+  <si>
+    <t>UI: Password Management</t>
+  </si>
+  <si>
+    <t>P14          </t>
+  </si>
+  <si>
+    <t>UI: Configuration Management</t>
+  </si>
+  <si>
+    <t>P15          </t>
+  </si>
+  <si>
+    <t>Security Event Logging</t>
+  </si>
+  <si>
+    <t>P16          </t>
+  </si>
+  <si>
+    <t>Security Event Notification</t>
+  </si>
+  <si>
+    <t>P17          </t>
+  </si>
+  <si>
+    <t>Application Update</t>
+  </si>
+  <si>
+    <t>P18          </t>
+  </si>
+  <si>
+    <t>Application Delivery Protection</t>
+  </si>
+  <si>
+    <t>P19          </t>
+  </si>
+  <si>
+    <t>Static Application Analysis</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>Physical Protection</t>
+  </si>
+  <si>
+    <t>最高風險</t>
+  </si>
+  <si>
+    <t>觸發測項</t>
+  </si>
+  <si>
+    <t>Recommendation</t>
+  </si>
+  <si>
+    <t>Recommendation_ch</t>
+  </si>
+  <si>
+    <t>EBPHKW6-D</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>package</t>
+  </si>
+  <si>
+    <t>issue</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>修正版本</t>
+  </si>
+  <si>
+    <t>建議版本</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>GHSA</t>
+  </si>
+  <si>
+    <t>Git</t>
+  </si>
+  <si>
+    <t>CCRL</t>
+  </si>
+  <si>
+    <t>1.02.00.00</t>
+  </si>
+  <si>
+    <t>未發現可確認之公開 CVE</t>
+  </si>
+  <si>
+    <t>1.07.00.00</t>
+  </si>
+  <si>
+    <t>風險值</t>
+  </si>
+  <si>
+    <t>影響範圍</t>
+  </si>
+  <si>
+    <t>CVE ID</t>
+  </si>
+  <si>
+    <t>漏洞類型</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>影響版本</t>
+  </si>
+  <si>
+    <t>風險</t>
+  </si>
+  <si>
+    <t>藍牙組織揭露</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>作業系統 (Android)</t>
+  </si>
+  <si>
+    <t>CVE-2020-0022</t>
+  </si>
+  <si>
+    <t>遠程代碼執行（RCE）</t>
+  </si>
+  <si>
+    <t>攻擊者可通過藍牙執行遠程代碼，控制設備。</t>
+  </si>
+  <si>
+    <t>藍牙4.2和5.x</t>
+  </si>
+  <si>
+    <t>敏感資料可被遠程訪問和竊取。</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>協議 (BR/EDR/LE)</t>
+  </si>
+  <si>
+    <t>CVE-2020-10134</t>
+  </si>
+  <si>
+    <t>中間人攻擊</t>
+  </si>
+  <si>
+    <t>攻擊者可以未經授權地完成藍牙設備之間的經驗證配對，從而可能訪問敏感的數據</t>
+  </si>
+  <si>
+    <t>藍牙4.2到5.1</t>
+  </si>
+  <si>
+    <t>利用確認號碼與密碼的不一致，欺騙用戶完成不安全的配對</t>
+  </si>
+  <si>
+    <t>✔</t>
+  </si>
+  <si>
+    <t>協議 (BR/EDR)</t>
+  </si>
+  <si>
+    <t>CVE-2020-10135</t>
+  </si>
+  <si>
+    <t>加密密鑰重設漏洞</t>
+  </si>
+  <si>
+    <t>允許攻擊者重新配對設備，篡改通信加密密鑰。</t>
+  </si>
+  <si>
+    <t>攻擊者可未經授權訪問設備並竊取數據。</t>
+  </si>
+  <si>
+    <t>CVE-2020-26558</t>
+  </si>
+  <si>
+    <t>藍牙2.1到5.1</t>
+  </si>
+  <si>
+    <t>協議 (LE)</t>
+  </si>
+  <si>
+    <t>CVE-2020-35473</t>
+  </si>
+  <si>
+    <t>訊息洩漏</t>
+  </si>
+  <si>
+    <t>如果一個 可解析私人地址（Resolvable Private Address, RPA）RPA 與特定的遠端設備建立了關聯，攻擊者可以通過發送主動掃描請求來識別該設備，這被稱為一種基於允許列表（allowlist）的側信道攻擊。</t>
+  </si>
+  <si>
+    <t>藍牙4.2到5.2</t>
+  </si>
+  <si>
+    <t>依賴 RPA 進行隱私保護的裝置，包括智能手機、穿戴設備、物聯網設備等造成隱私洩漏</t>
+  </si>
+  <si>
+    <t>CVE-2021-31615</t>
+  </si>
+  <si>
+    <t>在接收端設備的接收窗口內，攻擊者可注入經過設計的數據包。
+該數據包可在傳輸端設備開始其數據包傳輸之前成功攔截通信，實現中間人攻擊（MITM）。</t>
+  </si>
+  <si>
+    <t>攻擊者可實現完全中間人狀態，攔截並操控未加密通信</t>
+  </si>
+  <si>
+    <t>CVE-2021-34145</t>
+  </si>
+  <si>
+    <t>拒絕服務（DoS）攻擊</t>
+  </si>
+  <si>
+    <t>特製封包可導致設備崩潰，無法正常運作。</t>
+  </si>
+  <si>
+    <t>藍牙4.2及更新版本</t>
+  </si>
+  <si>
+    <t>設備崩潰，影響藍牙通信。</t>
+  </si>
+  <si>
+    <t>CVE-2021-37577</t>
+  </si>
+  <si>
+    <t>攻擊者在無需身份驗證的情況下，利用公鑰反射及密碼推測，冒充合法設備完成配對。</t>
+  </si>
+  <si>
+    <t>藍牙2.1到5.3</t>
+  </si>
+  <si>
+    <t>1.攻擊者可攔截並解碼配對設備之間的數據通信。
+2.攻擊者可冒充合法設備，執行未經授權的操作。</t>
+  </si>
+  <si>
+    <t>CVE-2022-24695</t>
+  </si>
+  <si>
+    <t>藍牙協議中的設計缺陷</t>
+  </si>
+  <si>
+    <t>攻擊者可通過高效的無線攻擊（over-the-air attack），獲取設備能力（Capabilities），其中可能包含設備擁有者的個人資訊</t>
+  </si>
+  <si>
+    <t>藍牙5.3及早期版本</t>
+  </si>
+  <si>
+    <t>1.設備隱私洩露：攻擊者可提取唯一標識符（如 MAC 地址）和其他設備信息。
+2.被動數據收集：攻擊者可通過收集的數據進行設備跟踪或識別。
+3.未授權連接風險：攻擊者可能利用 MAC 地址主動嘗試與目標設備建立連接。</t>
+  </si>
+  <si>
+    <t>CVE-2022-25836</t>
+  </si>
+  <si>
+    <t>藍牙4.0到5.3</t>
+  </si>
+  <si>
+    <t>攻擊者可以攔截並操控設備之間的配對過程，偽裝為合法設備。攻擊成功後，攻擊者可能：
+1.存取敏感數據。
+2.操控 BLE 設備進行未經授權的操作（例如智能家居設備、醫療設備或物聯網設備）。</t>
+  </si>
+  <si>
+    <t>CVE-2023-24023</t>
+  </si>
+  <si>
+    <t>藍牙會話密鑰派生過程</t>
+  </si>
+  <si>
+    <t>攻擊者可強制使用較短且容易預測的密鑰，從而解密過去和未來的通信內容</t>
+  </si>
+  <si>
+    <t>藍牙4.2到5.4</t>
+  </si>
+  <si>
+    <t>攻擊者可解密或操控設備之間的通信，即使使用了安全連接（Secure Connections）模式。</t>
+  </si>
+  <si>
+    <t>CVE-2024-33454</t>
+  </si>
+  <si>
+    <t>執行任意程式碼</t>
+  </si>
+  <si>
+    <t>此漏洞存在於 ESP-IDF v5.1 的藍牙堆疊中，特別是在處理 AVDTP（音訊/視訊分發傳輸協定）請求時，未正確驗證輸入資料的大小，導致緩衝區溢位。</t>
+  </si>
+  <si>
+    <t>藍牙5.0到5.1</t>
+  </si>
+  <si>
+    <t>攻擊者傳送特製的 AVDTP 封包，觸發記憶體損毀，導致設備重啟或執行未預期的程式碼。</t>
+  </si>
+  <si>
+    <t>作業系統 (Windows)</t>
+  </si>
+  <si>
+    <t>CVE-2025-27490</t>
+  </si>
+  <si>
+    <t>此漏洞源於 Windows 藍牙服務在處理來自藍牙設備的資料時，未正確驗證輸入大小，導致堆積緩衝區溢位。</t>
+  </si>
+  <si>
+    <t>攻擊者可利用此漏洞覆寫關鍵記憶體結構，進而執行任意程式碼或提升權限。</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 本次未執行 Source code scanning。
+測試結果：
+- 無提供，未取得執行本測項所需資料，因此判定為 Not Applicable。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 不適用；本測項未進入弱點驗證階段。
+可能影響：
+- 因未執行原始碼掃描，本次無法由此測項確認原始碼層級之潛在弱點。
+既有防護／限制條件：
+- 本次評估範圍受限於未提供本測項所需資料。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 依「SBOM」分頁所列軟體元件與版本進行公開弱點資訊檢視。
+測試結果：
+- SBOM 分頁所列 CCRL 1.02.00.00 與 1.07.00.00 均註記「未發現可確認之公開 CVE」。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 目前未發現可確認之公開 CVE，因此未識別明確的已知漏洞攻擊條件。
+可能影響：
+- 目前未發現可由已知公開 CVE 確認的元件弱點風險。
+既有防護／限制條件：
+- 本次結果以 SBOM 分頁已列元件、版本及可取得之公開 CVE 資訊為評估範圍。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 操作裝置並進行測量，觀察裝置執行期間是否出現異常。
+測試結果：
+- 測試過程未發生異常。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 本次測試未觀察到可進一步形成攻擊情境的異常行為。
+可能影響：
+- 本次測試未發現可確認之異常影響。
+既有防護／限制條件：
+- 原始資料未提供其他防護或限制條件。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 透過 nRF 進行藍牙配對及資料寫入，包含超長字串、特殊字元等異常輸入。
+測試結果：
+- 測試期間未發生系統當機，亦未發現其他異常。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 需能透過藍牙連線對裝置進行資料寫入。
+可能影響：
+- 本次異常輸入測試未觀察到可確認之系統異常或可利用行為。
+既有防護／限制條件：
+- 本次結果以已執行的藍牙配對與資料寫入測試案例為範圍。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 確認裝置是否具備可供主機弱點掃描之介面。
+測試結果：
+- 此裝置為 IoT 設備，未提供主機弱點掃描介面，因此本測項判定為 Not Applicable。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 不適用；未具備本測項所需之主機掃描介面。
+可能影響：
+- 本次未執行主機層弱點掃描，故無法由此測項評估主機服務弱點。
+既有防護／限制條件：
+- 評估範圍受限於裝置介面設計。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 確認裝置是否具有可進行 UI/Web 弱點掃描之介面。
+測試結果：
+- 裝置介面僅提供按鈕操作，無 Web 介面，因此本測項判定為 Not Applicable。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 不適用；裝置未提供 Web UI。
+可能影響：
+- 本次未識別 Web UI 相關攻擊面。
+既有防護／限制條件：
+- 使用介面僅限裝置按鈕操作。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 確認裝置是否具備可供遠端身分驗證之網路介面。
+測試結果：
+- 裝置無網路介面，因此本測項判定為 Not Applicable。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 不適用；未提供遠端網路介面。
+可能影響：
+- 本次未識別遠端網路身分驗證攻擊面。
+既有防護／限制條件：
+- 裝置無網路介面。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 確認裝置本地操作是否需要身分驗證。
+測試結果：
+- 裝置為單機使用情境，原始資料記載不需認證。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 原始資料未提供需透過帳號或本地身分驗證控制的使用情境。
+可能影響：
+- 本次未發現可由本地帳號認證機制確認之風險。
+既有防護／限制條件：
+- 裝置採單機使用，且原始資料未描述多使用者或帳號權限情境。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 確認裝置是否具有可進行遠端網路安全測試之介面。
+測試結果：
+- 裝置無網路介面，因此本測項判定為 Not Applicable。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 不適用；未提供遠端網路介面。
+可能影響：
+- 本次未識別遠端網路服務之攻擊面。
+既有防護／限制條件：
+- 裝置無網路介面。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
+- 確認裝置對外提供之網路／無線通訊服務，並參考 P06 藍牙測試結果。
+測試結果：
+- 裝置僅提供藍牙服務。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
+- 相關攻擊需透過裝置所提供的藍牙通訊介面，其他條件參考 P06。
+可能影響：
+- 本次未發現除藍牙外的其他網路服務攻擊面。
+既有防護／限制條件：
+- 對外服務範圍僅限藍牙，相關藍牙啟用與傳輸限制參考 P06。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 參考 F01，透過 nRF 進行藍牙配對及資料寫入，包含超長字串、特殊字元等異常輸入。
 測試結果：
 - 參考 F01：測試期間未發生系統當機，亦未發現其他異常。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 需能透過藍牙連線對裝置進行資料寫入。
 可能影響：
 - 本次異常輸入測試未觀察到可確認之輸入驗證異常或可利用行為。
 既有防護／限制條件：
 - 本次結果以 F01 已執行之藍牙資料寫入與異常輸入測試案例為範圍。</t>
-  </si>
-  <si>
-    <t>P11          </t>
-  </si>
-  <si>
-    <t>UI: Default Password</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認裝置是否具有帳號密碼與預設密碼功能。
 測試結果：
 - 裝置無帳號密碼設定功能，因此本測項判定為 Not Applicable。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 不適用；未提供帳號密碼功能。
 可能影響：
 - 本次未識別預設密碼相關攻擊面。
 既有防護／限制條件：
 - 裝置無帳號密碼設定功能。</t>
-  </si>
-  <si>
-    <t>P12          </t>
-  </si>
-  <si>
-    <t>UI: Password Strength</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認裝置是否具有帳號密碼設定及密碼強度要求。
 測試結果：
 - 裝置無帳號密碼設定功能，因此本測項判定為 Not Applicable。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 不適用；未提供帳號密碼功能。
 可能影響：
 - 本次未識別密碼強度相關攻擊面。
 既有防護／限制條件：
 - 裝置無帳號密碼設定功能。</t>
-  </si>
-  <si>
-    <t>P13          </t>
-  </si>
-  <si>
-    <t>UI: Password Management</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認裝置是否具有帳號密碼管理功能。
 測試結果：
 - 裝置無帳號密碼設定功能，因此本測項判定為 Not Applicable。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 不適用；未提供帳號密碼功能。
 可能影響：
 - 本次未識別密碼管理相關攻擊面。
 既有防護／限制條件：
 - 裝置無帳號密碼設定功能。</t>
-  </si>
-  <si>
-    <t>P14          </t>
-  </si>
-  <si>
-    <t>UI: Configuration Management</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認裝置使用介面可進行的設定與功能選項。
 測試結果：
 - 介面僅能依韌體設計選取對應功能，無法進行額外設定。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 原始資料未提供可由使用者任意修改安全設定的介面或情境。
 可能影響：
 - 本次未發現可由額外組態修改造成的可確認風險。
 既有防護／限制條件：
 - 使用者可操作之設定範圍受韌體既定功能限制。</t>
-  </si>
-  <si>
-    <t>P15          </t>
-  </si>
-  <si>
-    <t>Security Event Logging</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認產品是否具有 Security Event Logging 相關設計。
 測試結果：
 - 原始資料記載「無相關設計」，因此本測項判定為 Not Applicable。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 不適用；本次無相關日誌功能可供測試。
 可能影響：
 - 本次未針對安全事件日誌能力進行功能性驗證。
 既有防護／限制條件：
 - 產品目前無相關設計。</t>
-  </si>
-  <si>
-    <t>P16          </t>
-  </si>
-  <si>
-    <t>Security Event Notification</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認產品是否具有 Security Event Notification 相關設計。
 測試結果：
 - 原始資料記載「無相關設計」，因此本測項判定為 Not Applicable。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 不適用；本次無相關事件通知功能可供測試。
 可能影響：
 - 本次未針對安全事件通知能力進行功能性驗證。
 既有防護／限制條件：
 - 產品目前無相關設計。</t>
-  </si>
-  <si>
-    <t>P17          </t>
-  </si>
-  <si>
-    <t>Application Update</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認產品於 Application Update 測項之處理方式。
 測試結果：
 - 原始資料記載更新處理方式為「召回」。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 原始資料未提供可進一步判定之線上或本地更新攻擊情境。
 可能影響：
 - 因未提供其他更新流程細節，本次無法由此測項進一步評估更新機制之攻擊面。
 既有防護／限制條件：
 - 產品更新處理由召回方式進行；原始資料未提供其他更新機制資訊。</t>
-  </si>
-  <si>
-    <t>P18          </t>
-  </si>
-  <si>
-    <t>Application Delivery Protection</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認產品於 Application Delivery Protection 測項之處理方式。
 測試結果：
 - 原始資料記載處理方式為「召回」。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 原始資料未提供可進一步判定之應用程式交付或更新通道攻擊情境。
 可能影響：
 - 因未提供其他交付流程細節，本次無法由此測項進一步評估軟體交付保護之攻擊面。
 既有防護／限制條件：
 - 產品相關處理由召回方式進行；原始資料未提供其他交付保護機制資訊。</t>
-  </si>
-  <si>
-    <t>P19          </t>
-  </si>
-  <si>
-    <t>Static Application Analysis</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 針對 MCU 及藍牙韌體進行敏感性字串偵蒐。
 測試結果：
 - MCU 與藍牙韌體皆未發現敏感性關鍵字，因此原始資料評估為無風險。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 本次未發現可由敏感性字串暴露形成的明確攻擊情境。
 可能影響：
 - 本次未發現可確認之敏感性資訊字串暴露風險。
 既有防護／限制條件：
 - 本次結果以已執行之 MCU 與藍牙韌體敏感性字串偵蒐範圍為限。</t>
-  </si>
-  <si>
-    <t>P20</t>
-  </si>
-  <si>
-    <t>Physical Protection</t>
-  </si>
-  <si>
-    <t>測試方式：
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">測試方式：
 - 確認裝置是否具備防止韌體遭直接讀取之實體／晶片層保護設定。
 測試結果：
 - 廠商提供 Read Protection 防止韌體讀取設定，因此原始資料評估為無風險。
-攻擊條件：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：
 - 若攻擊者嘗試透過可接觸之裝置介面讀取韌體，將受到 Read Protection 設定限制。
 可能影響：
 - 本次未發現可確認之韌體直接讀取風險。
 既有防護／限制條件：
 - 已提供 Read Protection 防止韌體讀取。</t>
-  </si>
-  <si>
-    <t>最高風險</t>
-  </si>
-  <si>
-    <t>觸發測項</t>
-  </si>
-  <si>
-    <t>Recommendation</t>
-  </si>
-  <si>
-    <t>Recommendation_ch</t>
-  </si>
-  <si>
-    <t>EBPHKW6-D</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>package</t>
-  </si>
-  <si>
-    <t>issue</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>修正版本</t>
-  </si>
-  <si>
-    <t>建議版本</t>
-  </si>
-  <si>
-    <t>Risk</t>
-  </si>
-  <si>
-    <t>CVE</t>
-  </si>
-  <si>
-    <t>GHSA</t>
-  </si>
-  <si>
-    <t>Git</t>
-  </si>
-  <si>
-    <t>CCRL</t>
-  </si>
-  <si>
-    <t>1.02.00.00</t>
-  </si>
-  <si>
-    <t>未發現可確認之公開 CVE</t>
-  </si>
-  <si>
-    <t>1.07.00.00</t>
-  </si>
-  <si>
-    <t>風險值</t>
-  </si>
-  <si>
-    <t>影響範圍</t>
-  </si>
-  <si>
-    <t>CVE ID</t>
-  </si>
-  <si>
-    <t>漏洞類型</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>影響版本</t>
-  </si>
-  <si>
-    <t>風險</t>
-  </si>
-  <si>
-    <t>藍牙組織揭露</t>
-  </si>
-  <si>
-    <t>高</t>
-  </si>
-  <si>
-    <t>作業系統 (Android)</t>
-  </si>
-  <si>
-    <t>CVE-2020-0022</t>
-  </si>
-  <si>
-    <t>遠程代碼執行（RCE）</t>
-  </si>
-  <si>
-    <t>攻擊者可通過藍牙執行遠程代碼，控制設備。</t>
-  </si>
-  <si>
-    <t>藍牙4.2和5.x</t>
-  </si>
-  <si>
-    <t>敏感資料可被遠程訪問和竊取。</t>
-  </si>
-  <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>協議 (BR/EDR/LE)</t>
-  </si>
-  <si>
-    <t>CVE-2020-10134</t>
-  </si>
-  <si>
-    <t>中間人攻擊</t>
-  </si>
-  <si>
-    <t>攻擊者可以未經授權地完成藍牙設備之間的經驗證配對，從而可能訪問敏感的數據</t>
-  </si>
-  <si>
-    <t>藍牙4.2到5.1</t>
-  </si>
-  <si>
-    <t>利用確認號碼與密碼的不一致，欺騙用戶完成不安全的配對</t>
-  </si>
-  <si>
-    <t>✔</t>
-  </si>
-  <si>
-    <t>協議 (BR/EDR)</t>
-  </si>
-  <si>
-    <t>CVE-2020-10135</t>
-  </si>
-  <si>
-    <t>加密密鑰重設漏洞</t>
-  </si>
-  <si>
-    <t>允許攻擊者重新配對設備，篡改通信加密密鑰。</t>
-  </si>
-  <si>
-    <t>攻擊者可未經授權訪問設備並竊取數據。</t>
-  </si>
-  <si>
-    <t>CVE-2020-26558</t>
-  </si>
-  <si>
-    <t>藍牙2.1到5.1</t>
-  </si>
-  <si>
-    <t>協議 (LE)</t>
-  </si>
-  <si>
-    <t>CVE-2020-35473</t>
-  </si>
-  <si>
-    <t>訊息洩漏</t>
-  </si>
-  <si>
-    <t>如果一個 可解析私人地址（Resolvable Private Address, RPA）RPA 與特定的遠端設備建立了關聯，攻擊者可以通過發送主動掃描請求來識別該設備，這被稱為一種基於允許列表（allowlist）的側信道攻擊。</t>
-  </si>
-  <si>
-    <t>藍牙4.2到5.2</t>
-  </si>
-  <si>
-    <t>依賴 RPA 進行隱私保護的裝置，包括智能手機、穿戴設備、物聯網設備等造成隱私洩漏</t>
-  </si>
-  <si>
-    <t>CVE-2021-31615</t>
-  </si>
-  <si>
-    <t>在接收端設備的接收窗口內，攻擊者可注入經過設計的數據包。
-該數據包可在傳輸端設備開始其數據包傳輸之前成功攔截通信，實現中間人攻擊（MITM）。</t>
-  </si>
-  <si>
-    <t>攻擊者可實現完全中間人狀態，攔截並操控未加密通信</t>
-  </si>
-  <si>
-    <t>CVE-2021-34145</t>
-  </si>
-  <si>
-    <t>拒絕服務（DoS）攻擊</t>
-  </si>
-  <si>
-    <t>特製封包可導致設備崩潰，無法正常運作。</t>
-  </si>
-  <si>
-    <t>藍牙4.2及更新版本</t>
-  </si>
-  <si>
-    <t>設備崩潰，影響藍牙通信。</t>
-  </si>
-  <si>
-    <t>CVE-2021-37577</t>
-  </si>
-  <si>
-    <t>攻擊者在無需身份驗證的情況下，利用公鑰反射及密碼推測，冒充合法設備完成配對。</t>
-  </si>
-  <si>
-    <t>藍牙2.1到5.3</t>
-  </si>
-  <si>
-    <t>1.攻擊者可攔截並解碼配對設備之間的數據通信。
-2.攻擊者可冒充合法設備，執行未經授權的操作。</t>
-  </si>
-  <si>
-    <t>CVE-2022-24695</t>
-  </si>
-  <si>
-    <t>藍牙協議中的設計缺陷</t>
-  </si>
-  <si>
-    <t>攻擊者可通過高效的無線攻擊（over-the-air attack），獲取設備能力（Capabilities），其中可能包含設備擁有者的個人資訊</t>
-  </si>
-  <si>
-    <t>藍牙5.3及早期版本</t>
-  </si>
-  <si>
-    <t>1.設備隱私洩露：攻擊者可提取唯一標識符（如 MAC 地址）和其他設備信息。
-2.被動數據收集：攻擊者可通過收集的數據進行設備跟踪或識別。
-3.未授權連接風險：攻擊者可能利用 MAC 地址主動嘗試與目標設備建立連接。</t>
-  </si>
-  <si>
-    <t>CVE-2022-25836</t>
-  </si>
-  <si>
-    <t>藍牙4.0到5.3</t>
-  </si>
-  <si>
-    <t>攻擊者可以攔截並操控設備之間的配對過程，偽裝為合法設備。攻擊成功後，攻擊者可能：
-1.存取敏感數據。
-2.操控 BLE 設備進行未經授權的操作（例如智能家居設備、醫療設備或物聯網設備）。</t>
-  </si>
-  <si>
-    <t>CVE-2023-24023</t>
-  </si>
-  <si>
-    <t>藍牙會話密鑰派生過程</t>
-  </si>
-  <si>
-    <t>攻擊者可強制使用較短且容易預測的密鑰，從而解密過去和未來的通信內容</t>
-  </si>
-  <si>
-    <t>藍牙4.2到5.4</t>
-  </si>
-  <si>
-    <t>攻擊者可解密或操控設備之間的通信，即使使用了安全連接（Secure Connections）模式。</t>
-  </si>
-  <si>
-    <t>CVE-2024-33454</t>
-  </si>
-  <si>
-    <t>執行任意程式碼</t>
-  </si>
-  <si>
-    <t>此漏洞存在於 ESP-IDF v5.1 的藍牙堆疊中，特別是在處理 AVDTP（音訊/視訊分發傳輸協定）請求時，未正確驗證輸入資料的大小，導致緩衝區溢位。</t>
-  </si>
-  <si>
-    <t>藍牙5.0到5.1</t>
-  </si>
-  <si>
-    <t>攻擊者傳送特製的 AVDTP 封包，觸發記憶體損毀，導致設備重啟或執行未預期的程式碼。</t>
-  </si>
-  <si>
-    <t>作業系統 (Windows)</t>
-  </si>
-  <si>
-    <t>CVE-2025-27490</t>
-  </si>
-  <si>
-    <t>此漏洞源於 Windows 藍牙服務在處理來自藍牙設備的資料時，未正確驗證輸入大小，導致堆積緩衝區溢位。</t>
-  </si>
-  <si>
-    <t>攻擊者可利用此漏洞覆寫關鍵記憶體結構，進而執行任意程式碼或提升權限。</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>測試方式：
-- 本次未執行 Source code scanning。
-測試結果：
-- 無提供，未取得執行本測項所需資料，因此判定為 Not Applicable。
-攻擊條件：
-- 不適用；本測項未進入弱點驗證階段。
-可能影響：
-- 因未執行原始碼掃描，本次無法由此測項確認原始碼層級之潛在弱點。
-既有防護／限制條件：
-- 本次評估範圍受限於未提供本測項所需資料。</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -837,7 +1109,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1042,6 +1314,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="21">
@@ -1752,7 +2031,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
@@ -1776,7 +2055,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="25"/>
@@ -1788,19 +2067,19 @@
     </row>
     <row r="4" spans="1:12" ht="200.05" customHeight="1">
       <c r="A4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="C4" s="18" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>22</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -1812,19 +2091,19 @@
     </row>
     <row r="5" spans="1:12" ht="200.05" customHeight="1">
       <c r="A5" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
@@ -1836,19 +2115,19 @@
     </row>
     <row r="6" spans="1:12" ht="200.05" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
@@ -1860,19 +2139,19 @@
     </row>
     <row r="7" spans="1:12" ht="200.05" customHeight="1">
       <c r="A7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>32</v>
-      </c>
       <c r="C7" s="23" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
@@ -1884,19 +2163,19 @@
     </row>
     <row r="8" spans="1:12" ht="200.05" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
@@ -1908,19 +2187,19 @@
     </row>
     <row r="9" spans="1:12" ht="200.05" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>40</v>
+        <v>171</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
@@ -1932,19 +2211,19 @@
     </row>
     <row r="10" spans="1:12" ht="200.05" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="25"/>
@@ -1956,19 +2235,19 @@
     </row>
     <row r="11" spans="1:12" ht="200.05" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
@@ -1980,19 +2259,19 @@
     </row>
     <row r="12" spans="1:12" ht="200.05" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F12" s="25"/>
       <c r="G12" s="25"/>
@@ -2004,19 +2283,19 @@
     </row>
     <row r="13" spans="1:12" ht="200.05" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F13" s="25"/>
       <c r="G13" s="25"/>
@@ -2028,19 +2307,19 @@
     </row>
     <row r="14" spans="1:12" ht="200.05" customHeight="1">
       <c r="A14" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -2052,19 +2331,19 @@
     </row>
     <row r="15" spans="1:12" ht="200.05" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
@@ -2076,19 +2355,19 @@
     </row>
     <row r="16" spans="1:12" ht="200.05" customHeight="1">
       <c r="A16" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
@@ -2100,19 +2379,19 @@
     </row>
     <row r="17" spans="1:12" ht="200.05" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>65</v>
+        <v>176</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
@@ -2124,19 +2403,19 @@
     </row>
     <row r="18" spans="1:12" ht="200.05" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
@@ -2148,19 +2427,19 @@
     </row>
     <row r="19" spans="1:12" ht="200.05" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="F19" s="25"/>
       <c r="G19" s="25"/>
@@ -2172,19 +2451,19 @@
     </row>
     <row r="20" spans="1:12" ht="200.05" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="F20" s="25"/>
       <c r="G20" s="25"/>
@@ -2196,19 +2475,19 @@
     </row>
     <row r="21" spans="1:12" ht="200.05" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D21" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="F21" s="25"/>
       <c r="G21" s="25"/>
@@ -2220,19 +2499,19 @@
     </row>
     <row r="22" spans="1:12" ht="200.05" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
@@ -2244,19 +2523,19 @@
     </row>
     <row r="23" spans="1:12" ht="200.05" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D23" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="F23" s="25"/>
       <c r="G23" s="25"/>
@@ -2268,19 +2547,19 @@
     </row>
     <row r="24" spans="1:12" ht="200.05" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="F24" s="25"/>
       <c r="G24" s="25"/>
@@ -2292,19 +2571,19 @@
     </row>
     <row r="25" spans="1:12" ht="200.05" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D25" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="F25" s="25"/>
       <c r="G25" s="25"/>
@@ -9687,16 +9966,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9710,7 +9989,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="59"/>
       <c r="C3" s="59"/>
@@ -9719,7 +9998,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="59" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -9728,7 +10007,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="59" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5" s="59"/>
       <c r="C5" s="59"/>
@@ -9765,40 +10044,40 @@
   <sheetData>
     <row r="1" spans="2:13" ht="18.45" customHeight="1">
       <c r="B1" s="30" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D1" s="29"/>
     </row>
     <row r="2" spans="2:13" ht="15.9" customHeight="1">
       <c r="B2" s="36" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="K2" s="37" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>7</v>
@@ -9808,14 +10087,14 @@
     <row r="3" spans="2:13" ht="18" customHeight="1">
       <c r="B3" s="32"/>
       <c r="C3" s="33" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D3" s="34"/>
       <c r="E3" s="34" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="G3" s="34"/>
       <c r="H3" s="34"/>
@@ -9827,14 +10106,14 @@
     <row r="4" spans="2:13" ht="18" customHeight="1">
       <c r="B4" s="32"/>
       <c r="C4" s="33" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D4" s="34"/>
       <c r="E4" s="34" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="G4" s="34"/>
       <c r="H4" s="34"/>
@@ -9869,402 +10148,402 @@
   <sheetData>
     <row r="1" spans="1:9" s="38" customFormat="1" ht="18.45" customHeight="1">
       <c r="A1" s="38" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D1" s="40"/>
       <c r="E1" s="39" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="38" customFormat="1" ht="18.45" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D2" s="43" t="str">
         <f t="shared" ref="D2:D14" si="0">HYPERLINK(CONCATENATE("https://nvd.nist.gov/vuln/detail/", C2), "🔗")</f>
         <v>🔗</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="H2" s="42" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="30.9" customHeight="1">
       <c r="A3" s="44" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D3" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="38" customFormat="1" ht="18.45" customHeight="1">
       <c r="A4" s="42" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D4" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="G4" s="42" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:9" s="38" customFormat="1" ht="30.9" customHeight="1">
       <c r="A5" s="44" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D5" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="H5" s="50" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="I5" s="42" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="77.150000000000006" customHeight="1">
       <c r="A6" s="44" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D6" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="H6" s="50" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9" ht="61.75" customHeight="1">
       <c r="A7" s="44" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D7" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E7" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="G7" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="H7" s="48" t="s">
-        <v>147</v>
-      </c>
       <c r="I7" s="42" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.45" customHeight="1">
       <c r="A8" s="42" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D8" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="H8" s="53" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="I8" s="42"/>
     </row>
     <row r="9" spans="1:9" ht="30.9" customHeight="1">
       <c r="A9" s="44" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D9" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="G9" s="48" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="92.6" customHeight="1">
       <c r="A10" s="42" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D10" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H10" s="53" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="I10" s="42"/>
     </row>
     <row r="11" spans="1:9" ht="77.150000000000006" customHeight="1">
       <c r="A11" s="54" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D11" s="47" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="G11" s="48" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30.9" customHeight="1">
       <c r="A12" s="42" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="D12" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G12" s="42" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:9" ht="46.3" customHeight="1">
       <c r="A13" s="42" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D13" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="G13" s="42" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9" ht="46.3" customHeight="1">
       <c r="A14" s="42" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D14" s="43" t="str">
         <f t="shared" si="0"/>
         <v>🔗</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G14" s="42" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="H14" s="53" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="I14" s="42"/>
     </row>
@@ -10310,22 +10589,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="14.15" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="14.15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="14.15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="14.15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="14.15" customHeight="1">
@@ -10340,12 +10619,12 @@
     </row>
     <row r="7" spans="1:1" ht="14.15" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="14.15" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14.15" customHeight="1">
